--- a/downloads/pricing-calculator/en.xlsx
+++ b/downloads/pricing-calculator/en.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Free from Lokalfleet · lokalfleet.com</t>
+          <t>Free from RoveHQ · rovehq.io</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Lokalfleet tracks real bookings, payments and costs per vehicle automatically, so you can check these numbers against what actually happens: lokalfleet.com</t>
+          <t>RoveHQ tracks real bookings, payments and costs per vehicle automatically, so you can check these numbers against what actually happens: rovehq.io</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Free from Lokalfleet · lokalfleet.com</t>
+          <t>Free from RoveHQ · rovehq.io</t>
         </is>
       </c>
     </row>
